--- a/data/processed_data/Video_341/contracciones_Video_341.xlsx
+++ b/data/processed_data/Video_341/contracciones_Video_341.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,22 +425,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -795,317 +783,317 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1133,7 +1121,7 @@
         <v>0.1025959199999505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1190639264044187</v>
+        <v>0.1190639264039973</v>
       </c>
       <c r="H2" t="n">
         <v>22</v>
@@ -1164,8 +1152,8 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 22, 'fuente_tiempo': 'inicio (onset 10 %) en 22 de 22 eventos; pico en el resto', 'modo_busqueda': 'libre', 'trenes':    tren busqueda                                          veredicto  ... n_sacados_tiempo_amplitud  inicio_s  fin_s
-0     1    libre  no se encontro un tren periodico que se distin...  ...                         0     0.829   7.28
+          <t>{'n_eventos': 22, 'fuente_tiempo': 'inicio (onset 10 %) en 22 de 22 eventos; pico en el resto', 'modo_busqueda': 'libre', 'trenes':    tren busqueda  ... inicio_s fin_s
+0     1    libre  ...    0.829  7.28
 [1 rows x 17 columns], 'dudosos': Empty DataFrame
 Columns: []
 Index: [], 'sacados_tiempo_amplitud': Empty DataFrame
@@ -1176,8 +1164,8 @@
        'espontaneos', 'espontaneos', 'espontaneos', 'espontaneos',
        'espontaneos', 'espontaneos', 'espontaneos', 'espontaneos',
        'espontaneos', 'espontaneos'], dtype=object), 'tren_por_evento': array([0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]), 'estimulados': array([], dtype=int64), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([ 0,  1,  2,  3,  4,  5,  6,  7,  8,  9, 10, 11, 12, 13, 14, 15, 16,
-       17, 18, 19, 20, 21]), 'hay_estimulacion': False, 'n_trenes_estimulados': 0, 'tren_principal': 1, 'veredicto': 'no se encontro un tren periodico que se distinga del azar', 'z': 4.044, 'p_valor': 0.967032967032967, 'periodo_grilla_s': 0.7988, 'periodo_s': 0.8084, 'periodo_err_s': 0.00501, 'frecuencia_Hz': 1.23702, 'frecuencia_err_Hz': 0.007662, 'jitter_s': 0.01914, 'tolerancia_s': 0.0667, 'n_estimulados': 7, 'n_ranuras': 9, 'tasa_captura_pct': 77.8, 'tren_inicio_s': 0.829, 'tren_fin_s': 7.28, 'motivo': 'no se encontro un tren periodico que se distinga del azar (mejor intento: T=0.808 s, z=4.04, p=0.967)', 'resumen_grupos':          grupo   n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
-0  espontaneos  22        0.53  ...             269.3               0.9956           0.1081
+       17, 18, 19, 20, 21]), 'hay_estimulacion': False, 'n_trenes_estimulados': 0, 'tren_principal': 1, 'veredicto': 'no se encontro un tren periodico que se distinga del azar', 'z': 4.044, 'p_valor': 0.967032967032967, 'periodo_grilla_s': 0.7988, 'periodo_s': 0.8084, 'periodo_err_s': 0.00501, 'frecuencia_Hz': 1.23702, 'frecuencia_err_Hz': 0.007662, 'jitter_s': 0.01914, 'tolerancia_s': 0.0667, 'n_estimulados': 7, 'n_ranuras': 9, 'tasa_captura_pct': 77.8, 'tren_inicio_s': 0.829, 'tren_fin_s': 7.28, 'motivo': 'no se encontro un tren periodico que se distinga del azar (mejor intento: T=0.808 s, z=4.04, p=0.967)', 'resumen_grupos':          grupo   n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  espontaneos  22  ...               0.9956           0.1081
 [1 rows x 10 columns], 'espontaneas_instantanea':     tiempo_s  intervalo_s  frecuencia_Hz
 0      0.678       0.3018         3.3133
 1      1.102       0.5466         1.8296
@@ -1215,25 +1203,25 @@
         <v>30.00000000000171</v>
       </c>
       <c r="S2" t="n">
-        <v>0.295863717462375</v>
+        <v>0.2958637174623361</v>
       </c>
       <c r="T2" t="n">
-        <v>10.83149266469093</v>
+        <v>10.83149266472785</v>
       </c>
       <c r="U2" t="n">
         <v>-0.03333333333333144</v>
       </c>
       <c r="V2" t="n">
-        <v>29.76622239523591</v>
+        <v>29.766222395232</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.06286604196335943</v>
+        <v>-0.06286604196378477</v>
       </c>
       <c r="X2" t="n">
-        <v>3.986330895992797</v>
+        <v>3.986330896033876</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6.324819421048346</v>
+        <v>-6.324819421091139</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -1247,7 +1235,7 @@
         <v>22</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.394168244986029</v>
+        <v>0.3941682449860308</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -1365,52 +1353,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1465,87 +1453,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1625,32 +1613,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1843,17 +1831,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>intervalo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
@@ -2105,27 +2093,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -2520,117 +2508,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2658,10 +2646,10 @@
         <v>1.072400000000016</v>
       </c>
       <c r="G2" t="n">
-        <v>252.6136217480704</v>
+        <v>252.6136217480703</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4245218419256552</v>
+        <v>0.4245218419256553</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -2731,10 +2719,10 @@
         <v>1.004500000000007</v>
       </c>
       <c r="G3" t="n">
-        <v>252.6149478409012</v>
+        <v>252.6149478409015</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3976407606063949</v>
+        <v>0.3976407606063944</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -2804,10 +2792,10 @@
         <v>1.128600000000006</v>
       </c>
       <c r="G4" t="n">
-        <v>252.6122956552396</v>
+        <v>252.6122956552392</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4467716019414579</v>
+        <v>0.4467716019414586</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -2877,10 +2865,10 @@
         <v>1.286000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>252.5996117942299</v>
+        <v>252.5996117942253</v>
       </c>
       <c r="H5" t="n">
-        <v>0.509106087244342</v>
+        <v>0.5091060872443514</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -3023,10 +3011,10 @@
         <v>1.009399999999971</v>
       </c>
       <c r="G7" t="n">
-        <v>252.5694499119771</v>
+        <v>252.5694499119773</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3996524521678123</v>
+        <v>0.399652452167812</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -3169,10 +3157,10 @@
         <v>0.9867000000000417</v>
       </c>
       <c r="G9" t="n">
-        <v>252.5494715803666</v>
+        <v>252.549471580364</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3906957293656632</v>
+        <v>0.3906957293656672</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -3242,10 +3230,10 @@
         <v>1.038400000000024</v>
       </c>
       <c r="G10" t="n">
-        <v>252.616673109812</v>
+        <v>252.6166731098115</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4110575866655617</v>
+        <v>0.4110575866655625</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -3315,10 +3303,10 @@
         <v>1.130100000000027</v>
       </c>
       <c r="G11" t="n">
-        <v>252.5742363643654</v>
+        <v>252.574236364365</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4474328087722046</v>
+        <v>0.4474328087722054</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -3461,10 +3449,10 @@
         <v>0.9311999999999898</v>
       </c>
       <c r="G13" t="n">
-        <v>252.5741737911605</v>
+        <v>252.5741737911584</v>
       </c>
       <c r="H13" t="n">
-        <v>0.368683775550998</v>
+        <v>0.3686837755510011</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -3534,10 +3522,10 @@
         <v>0.9690000000000509</v>
       </c>
       <c r="G14" t="n">
-        <v>252.583469954938</v>
+        <v>252.5834699549349</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3836355562669738</v>
+        <v>0.3836355562669784</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -3607,10 +3595,10 @@
         <v>1.111500000000035</v>
       </c>
       <c r="G15" t="n">
-        <v>252.6412043467045</v>
+        <v>252.6412043467042</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4399519875921354</v>
+        <v>0.439951987592136</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -3680,10 +3668,10 @@
         <v>0.9733999999999696</v>
       </c>
       <c r="G16" t="n">
-        <v>252.9544652955036</v>
+        <v>252.9544652955028</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3848123411709041</v>
+        <v>0.3848123411709053</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -3753,10 +3741,10 @@
         <v>0.9161000000000286</v>
       </c>
       <c r="G17" t="n">
-        <v>252.9456022808475</v>
+        <v>252.9456022808467</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3621727326901202</v>
+        <v>0.3621727326901214</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
@@ -3826,10 +3814,10 @@
         <v>1.011300000000006</v>
       </c>
       <c r="G18" t="n">
-        <v>252.9577443467616</v>
+        <v>252.9577443467596</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3997900924565833</v>
+        <v>0.3997900924565864</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -3899,10 +3887,10 @@
         <v>0.942799999999977</v>
       </c>
       <c r="G19" t="n">
-        <v>252.9151674949146</v>
+        <v>252.9151674949136</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3727732145676609</v>
+        <v>0.3727732145676624</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -3972,10 +3960,10 @@
         <v>0.8797000000000139</v>
       </c>
       <c r="G20" t="n">
-        <v>252.8603261514737</v>
+        <v>252.8603261514725</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3478995749902804</v>
+        <v>0.3478995749902821</v>
       </c>
       <c r="I20" t="n">
         <v>2</v>
@@ -4045,10 +4033,10 @@
         <v>0.9051999999999794</v>
       </c>
       <c r="G21" t="n">
-        <v>252.8663869996332</v>
+        <v>252.8663869996323</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3579756134219976</v>
+        <v>0.3579756134219989</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -4118,10 +4106,10 @@
         <v>0.8804999999999836</v>
       </c>
       <c r="G22" t="n">
-        <v>252.9142774428701</v>
+        <v>252.9142774428677</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3481416742868052</v>
+        <v>0.3481416742868085</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
@@ -4191,10 +4179,10 @@
         <v>0.8959999999999582</v>
       </c>
       <c r="G23" t="n">
-        <v>252.8617874879591</v>
+        <v>252.8617874879584</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3543437736880763</v>
+        <v>0.3543437736880772</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -4257,112 +4245,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -4381,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>0.394168244986029</v>
+        <v>0.3941682449860308</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4447,7 +4435,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>0.394168244986029</v>
+        <v>0.3941682449860308</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/data/processed_data/Video_341/contracciones_Video_341.xlsx
+++ b/data/processed_data/Video_341/contracciones_Video_341.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_341" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_341" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_341" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="trenes_Video_341" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="grilla_Video_341" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="espont_Video_341" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="eventos_Video_341" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cinetica_Video_341" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cin_grupos_Video_341" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_341" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_341" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_341" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trenes_Video_341" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_341" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="espont_Video_341" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_341" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_341" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_341" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_341" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,13 +774,311 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3941682449860308</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.3697-0.4126</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.3748-0.408</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9956000000000245</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1016666666666668</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>22</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.100000000000005</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3941682449860308</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.3697-0.4126</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.3748-0.408</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9956000000000245</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1016666666666668</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.100000000000005</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK2"/>
+  <dimension ref="A1:BU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,167 +1234,217 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1242,100 +1591,132 @@
           <t>0.3697-0.4126</t>
         </is>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.3748-0.408</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9956000000000245</v>
+      </c>
+      <c r="AG2" t="n">
         <v>22</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.1016666666666668</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>22</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
         <v>0.100000000000005</v>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
         </is>
       </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="n">
         <v>0.3333333333333144</v>
       </c>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1.5 s: sin meseta | 2 s: sin meseta | 3 s: sin meseta</t>
         </is>
       </c>
-      <c r="BF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr">
+      <c r="BJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>no hay meseta en el escaneo de k</t>
         </is>
       </c>
-      <c r="BI2" t="n">
+      <c r="BM2" t="n">
         <v>0.07665042000005838</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BN2" t="n">
         <v>0.1460361000000863</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BO2" t="n">
         <v>1.905222437137005</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.9743100000000483</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.3857186174984567</v>
+      </c>
+      <c r="BT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>no contable (conteo NO reportable); actividad basal 0.39 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,6 +2499,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2135,6 +2526,12 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2151,6 +2548,12 @@
       </c>
       <c r="E3" t="b">
         <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2169,6 +2572,12 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2186,6 +2595,12 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2203,6 +2618,12 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2220,6 +2641,12 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2237,6 +2664,12 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2254,6 +2687,12 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2271,6 +2710,12 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2288,6 +2733,12 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2305,6 +2756,12 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2322,6 +2779,12 @@
       <c r="E13" t="b">
         <v>0</v>
       </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2339,6 +2802,12 @@
       <c r="E14" t="b">
         <v>0</v>
       </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2356,6 +2825,12 @@
       <c r="E15" t="b">
         <v>0</v>
       </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2373,6 +2848,12 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2390,6 +2871,12 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2894,12 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2424,6 +2917,12 @@
       <c r="E19" t="b">
         <v>0</v>
       </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2441,6 +2940,12 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2458,6 +2963,12 @@
       <c r="E21" t="b">
         <v>0</v>
       </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2475,6 +2986,12 @@
       <c r="E22" t="b">
         <v>0</v>
       </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2490,6 +3007,12 @@
         <v>0</v>
       </c>
       <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2504,1730 +3027,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tren</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.5733333333333334</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.072400000000016</v>
-      </c>
-      <c r="G2" t="n">
-        <v>252.6136217480703</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.4245218419256553</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5273629244874654</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.045970408845868</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.1283333333333333</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.05777547256800386</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1016666666666667</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.6639490409715135</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1365861164840482</v>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8750000000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.004500000000007</v>
-      </c>
-      <c r="G3" t="n">
-        <v>252.6149478409015</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.3976407606063944</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8291756413988099</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.04582435860119016</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.1016666666666667</v>
-      </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.03507246376811668</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1050000000000001</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.9548662207357844</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1256905793369745</v>
+          <t>0-10 s</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>42</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.406666666666667</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.128600000000006</v>
-      </c>
-      <c r="G4" t="n">
-        <v>252.6122956552392</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.4467716019414586</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.375741659455821</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.03092500721084579</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.09833333333333294</v>
-      </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.05366976787895705</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.09833333333333294</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.485045189879939</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1093035304241177</v>
+          <t>0.9743100000000483</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.286000000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>252.5996117942253</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.5091060872443514</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.657063526675389</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.05293647332461049</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1016666666666659</v>
-      </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.04933616911575145</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.09666666666666712</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.813675889328065</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1566123626526759</v>
+          <t>0.3857186174984567</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2.285</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9519000000000233</v>
-      </c>
-      <c r="G6" t="n">
-        <v>252.5596060028137</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3769011264570228</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.212349921816576</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0726500781834245</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.101666666666667</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.01383345789736001</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.101666666666667</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.311304027652542</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.0989541058359662</v>
+          <t>False</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>84</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.806666666666667</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.009399999999971</v>
-      </c>
-      <c r="G7" t="n">
-        <v>252.5694499119773</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.399652452167812</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.76746895976652</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.03919770690014746</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.09833333333333272</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.04643166089965423</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.100000000000001</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.883981293778328</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1165123340118082</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>101</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.373333333333334</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.04340000000002</v>
-      </c>
-      <c r="G8" t="n">
-        <v>252.5960520959159</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4130705889274229</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.317165981451382</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.05616735188195232</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.1000000000000001</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.02912454323994984</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1000000000000001</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.433129745971044</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.1159637645196621</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>109</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9867000000000417</v>
-      </c>
-      <c r="G9" t="n">
-        <v>252.549471580364</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.3906957293656672</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.593642009527934</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.04635799047206612</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.106666666666666</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.05741211105380772</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.101666666666667</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.735764761904762</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.142122752376828</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>125</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.173333333333334</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.038400000000024</v>
-      </c>
-      <c r="G10" t="n">
-        <v>252.6166731098115</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4110575866655625</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.120296256396445</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.05303707693688864</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.1016666666666666</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.0397918376278783</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>4.234712347502598</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.1144160911061531</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>133</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.130100000000027</v>
-      </c>
-      <c r="G11" t="n">
-        <v>252.574236364365</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4474328087722054</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.400091908091908</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.0399080919080923</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.09833333333333361</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.04867094017093976</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1066666666666674</v>
-      </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4.528073022049287</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.1279811139573788</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>149</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4.973333333333334</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.022600000000011</v>
-      </c>
-      <c r="G12" t="n">
-        <v>252.5415771949008</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4049234234451669</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.924614778325124</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.0487185550082101</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1083333333333334</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.03460715832792083</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.06833333333333336</v>
-      </c>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5.034282460136676</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.1096676818115521</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>173</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.773333333333333</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9311999999999898</v>
-      </c>
-      <c r="G13" t="n">
-        <v>252.5741737911584</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3686837755510011</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.729447979363715</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.04388535396961846</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.331666666666667</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.2055029980013376</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2983333333333338</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6.040100470879803</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.3106524915160875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>214</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7.306666666666668</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9690000000000509</v>
-      </c>
-      <c r="G14" t="n">
-        <v>252.5834699549349</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.3836355562669784</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7.280246599412281</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.02642006725438772</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.07166666666666721</v>
-      </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.04980469607197424</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1000000000000005</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>7.419205741138011</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.1389591417257305</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>229</v>
-      </c>
-      <c r="E15" t="n">
-        <v>7.815</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.111500000000035</v>
-      </c>
-      <c r="G15" t="n">
-        <v>252.6412043467042</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.439951987592136</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7.538700181159422</v>
-      </c>
-      <c r="K15" t="n">
-        <v>9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.2762998188405783</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2333333333333334</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3616666666666664</v>
-      </c>
-      <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.0460195136824435</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.1016666666666666</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>7.880225999330991</v>
-      </c>
-      <c r="V15" t="n">
-        <v>12</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.3415258181715686</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E16" t="n">
-        <v>36.01166666666667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9733999999999696</v>
-      </c>
-      <c r="G16" t="n">
-        <v>252.9544652955028</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.3848123411709053</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>35.95041779788839</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.06124886877827862</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.1350000000000051</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.05517204301074941</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.1016666666666595</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>36.11016558675306</v>
-      </c>
-      <c r="V16" t="n">
-        <v>6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.1597477888646637</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1085</v>
-      </c>
-      <c r="E17" t="n">
-        <v>36.34833333333334</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.9161000000000286</v>
-      </c>
-      <c r="G17" t="n">
-        <v>252.9456022808467</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.3621727326901214</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>36.30437881578948</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0439545175438667</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.1283333333333374</v>
-      </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.05747242278379616</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.1000000000000085</v>
-      </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>36.45853710045662</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.1541582846671474</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1145</v>
-      </c>
-      <c r="E18" t="n">
-        <v>38.34666666666667</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.011300000000006</v>
-      </c>
-      <c r="G18" t="n">
-        <v>252.9577443467596</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.3997900924565864</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38.29145163506458</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.05521503160208852</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.04423604145770099</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>38.42766579569491</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1362141606303311</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1165</v>
-      </c>
-      <c r="E19" t="n">
-        <v>39.01333333333334</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.942799999999977</v>
-      </c>
-      <c r="G19" t="n">
-        <v>252.9151674949136</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.3727732145676624</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>38.94854818350571</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.06478514982763528</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.1049999999999969</v>
-      </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.04787015043546461</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>39.09231870716989</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.1437705236641875</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1214</v>
-      </c>
-      <c r="E20" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.8797000000000139</v>
-      </c>
-      <c r="G20" t="n">
-        <v>252.8603261514725</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.3478995749902821</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>40.5853205903431</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.05467940965689877</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1049999999999969</v>
-      </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.03873623954205385</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.1049999999999969</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>40.7139661089661</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1286455186230029</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1233</v>
-      </c>
-      <c r="E21" t="n">
-        <v>41.27333333333333</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9051999999999794</v>
-      </c>
-      <c r="G21" t="n">
-        <v>252.8663869996323</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.3579756134219989</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41.21303783857357</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.06029549475976381</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.04198150203477979</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1099999999999994</v>
-      </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>41.34810478151453</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.1350669429409592</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1295</v>
-      </c>
-      <c r="E22" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8804999999999836</v>
-      </c>
-      <c r="G22" t="n">
-        <v>252.9142774428677</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3481416742868085</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>43.47274863917337</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.07725136082662942</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.02003608347962427</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>43.59752269779508</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1247740586217105</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1389</v>
-      </c>
-      <c r="E23" t="n">
-        <v>46.67833333333333</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.8959999999999582</v>
-      </c>
-      <c r="G23" t="n">
-        <v>252.8617874879584</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.3543437736880772</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>46.62544537672685</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.05288795660647594</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.08833333333332405</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.04447735191638458</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>46.75795681937862</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.1325114426517686</v>
+          <t>no contable (conteo NO reportable); actividad basal 0.39 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4241,251 +3125,1943 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cinetica_min_frames</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_eventos_cinetica</t>
+          <t>tren</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_iqr_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ttp_n_eventos</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ttp_n_medibles</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ttp_frames_mediana</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ttp_reportable</t>
+          <t>meseta_pico_frames</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>frame_llega_max</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_iqr_s</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_cota_inf_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_cota_sup_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>rt50_n_eventos</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_n_medibles</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>rt50_frames_mediana</t>
+          <t>ttp_min_s</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>rt50_reportable</t>
+          <t>ttp_max_s</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_iqr_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_cota_inf_s</t>
-        </is>
-      </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>rt50_cota_sup_s</t>
+          <t>rt50_min_s</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>cinetica_motivo</t>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>todos</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5733333333333334</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.072400000000016</v>
+      </c>
+      <c r="G2" t="n">
+        <v>252.6136217480703</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4245218419256553</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5733333333333334</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.5273629244874654</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.045970408845868</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1283333333333333</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.05777547256800386</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1016666666666667</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.6639490409715135</v>
+      </c>
+      <c r="Y2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="Z2" t="n">
+        <v>0.1365861164840482</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8750000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.004500000000007</v>
+      </c>
+      <c r="G3" t="n">
+        <v>252.6149478409015</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3976407606063944</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8750000000000001</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8291756413988099</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04582435860119016</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1016666666666667</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03507246376811668</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1050000000000001</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9548662207357844</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1256905793369745</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.406666666666667</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.128600000000006</v>
+      </c>
+      <c r="G4" t="n">
+        <v>252.6122956552392</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4467716019414586</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>42</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.406666666666667</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.375741659455821</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03092500721084579</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.09833333333333294</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.05366976787895705</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.09833333333333294</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.485045189879939</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1093035304241177</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>51</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.286000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>252.5996117942253</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5091060872443514</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.657063526675389</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.05293647332461049</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1016666666666659</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.04933616911575145</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.09666666666666712</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.813675889328065</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1566123626526759</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>68</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.285</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9519000000000233</v>
+      </c>
+      <c r="G6" t="n">
+        <v>252.5596060028137</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3769011264570228</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.212349921816576</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02765007818342458</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.101666666666667</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05883345789735994</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.101666666666667</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.311304027652542</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0989541058359662</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.806666666666667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.009399999999971</v>
+      </c>
+      <c r="G7" t="n">
+        <v>252.5694499119773</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.399652452167812</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>84</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.806666666666667</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.76746895976652</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03919770690014746</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.09833333333333272</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.04643166089965423</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.100000000000001</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.883981293778328</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1165123340118082</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>101</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.373333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04340000000002</v>
+      </c>
+      <c r="G8" t="n">
+        <v>252.5960520959159</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4130705889274229</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>101</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.373333333333334</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.317165981451382</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05616735188195232</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.02912454323994984</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.433129745971044</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1159637645196621</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>109</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9867000000000417</v>
+      </c>
+      <c r="G9" t="n">
+        <v>252.549471580364</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3906957293656672</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>109</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.593642009527934</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04635799047206612</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.106666666666666</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05741211105380772</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.101666666666667</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.735764761904762</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.142122752376828</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>125</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.173333333333334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.038400000000024</v>
+      </c>
+      <c r="G10" t="n">
+        <v>252.6166731098115</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4110575866655625</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.173333333333334</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.120296256396445</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05303707693688864</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.0397918376278783</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.234712347502598</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1144160911061531</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>133</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.130100000000027</v>
+      </c>
+      <c r="G11" t="n">
+        <v>252.574236364365</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4474328087722054</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>133</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.400091908091908</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0399080919080923</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.09833333333333361</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.04867094017093976</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1066666666666674</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4.528073022049287</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1279811139573788</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>149</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.973333333333334</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.022600000000011</v>
+      </c>
+      <c r="G12" t="n">
+        <v>252.5415771949008</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4049234234451669</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>149</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.973333333333334</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.924614778325124</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0487185550082101</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1083333333333334</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.03460715832792083</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.06833333333333336</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.034282460136676</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1096676818115521</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>173</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.773333333333333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9311999999999898</v>
+      </c>
+      <c r="G13" t="n">
+        <v>252.5741737911584</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3686837755510011</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>173</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.773333333333333</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.729447979363715</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04388535396961846</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.331666666666667</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2055029980013376</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2983333333333338</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.040100470879803</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.3106524915160875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>214</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.306666666666668</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9690000000000509</v>
+      </c>
+      <c r="G14" t="n">
+        <v>252.5834699549349</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3836355562669784</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>214</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7.306666666666668</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7.280246599412281</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.02642006725438772</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07166666666666721</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.04980469607197424</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7.419205741138011</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.1389591417257305</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>229</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7.815</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.111500000000035</v>
+      </c>
+      <c r="G15" t="n">
+        <v>252.6412043467042</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.439951987592136</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>229</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.815</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.538700181159422</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2762998188405783</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.2333333333333334</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3616666666666664</v>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.0460195136824435</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1016666666666666</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>7.880225999330991</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.3415258181715686</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.01166666666667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9733999999999696</v>
+      </c>
+      <c r="G16" t="n">
+        <v>252.9544652955028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3848123411709053</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1075</v>
+      </c>
+      <c r="K16" t="n">
+        <v>36.01166666666667</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>35.95041779788839</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06124886877827862</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1350000000000051</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.05517204301074941</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>36.11016558675306</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1597477888646637</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36.34833333333334</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9161000000000286</v>
+      </c>
+      <c r="G17" t="n">
+        <v>252.9456022808467</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3621727326901214</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1085</v>
+      </c>
+      <c r="K17" t="n">
+        <v>36.34833333333334</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36.30437881578948</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0439545175438667</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1283333333333374</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.05747242278379616</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1000000000000085</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>36.45853710045662</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.1541582846671474</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E18" t="n">
+        <v>38.34666666666667</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.011300000000006</v>
+      </c>
+      <c r="G18" t="n">
+        <v>252.9577443467596</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3997900924565864</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1145</v>
+      </c>
+      <c r="K18" t="n">
+        <v>38.34666666666667</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>38.29145163506458</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05521503160208852</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.04423604145770099</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>38.42766579569491</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1362141606303311</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E19" t="n">
+        <v>39.01333333333334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.942799999999977</v>
+      </c>
+      <c r="G19" t="n">
+        <v>252.9151674949136</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3727732145676624</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1165</v>
+      </c>
+      <c r="K19" t="n">
+        <v>39.01333333333334</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>38.94854818350571</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06478514982763528</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.04787015043546461</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>39.09231870716989</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.1437705236641875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1214</v>
+      </c>
+      <c r="E20" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8797000000000139</v>
+      </c>
+      <c r="G20" t="n">
+        <v>252.8603261514725</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3478995749902821</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1214</v>
+      </c>
+      <c r="K20" t="n">
+        <v>40.64</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>40.5853205903431</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.05467940965689877</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.03873623954205385</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>40.7139661089661</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.1286455186230029</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1233</v>
+      </c>
+      <c r="E21" t="n">
+        <v>41.27333333333333</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9051999999999794</v>
+      </c>
+      <c r="G21" t="n">
+        <v>252.8663869996323</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3579756134219989</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1233</v>
+      </c>
+      <c r="K21" t="n">
+        <v>41.27333333333333</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>41.21303783857357</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06029549475976381</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.04198150203477979</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.1099999999999994</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>41.34810478151453</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.1350669429409592</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E22" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8804999999999836</v>
+      </c>
+      <c r="G22" t="n">
+        <v>252.9142774428677</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3481416742868085</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1294</v>
+      </c>
+      <c r="K22" t="n">
+        <v>43.50666666666667</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>43.47274863917337</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.03391802749329997</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.06336941681295372</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>43.59752269779508</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.1247740586217105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.3941682449860308</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.3697-0.4126</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>22</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1016666666666668</v>
-      </c>
-      <c r="N2" t="n">
-        <v>22</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.100000000000005</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>espontaneos</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1389</v>
+      </c>
+      <c r="E23" t="n">
+        <v>46.67833333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.8959999999999582</v>
+      </c>
+      <c r="G23" t="n">
+        <v>252.8617874879584</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3543437736880772</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1389</v>
+      </c>
+      <c r="K23" t="n">
+        <v>46.67833333333333</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>46.62544537672685</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.05288795660647594</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.08833333333332405</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.04447735191638458</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>46.75795681937862</v>
+      </c>
+      <c r="Y23" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3941682449860308</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.3697-0.4126</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1016666666666668</v>
-      </c>
-      <c r="N3" t="n">
-        <v>22</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.100000000000005</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
-        </is>
+      <c r="Z23" t="n">
+        <v>0.1325114426517686</v>
       </c>
     </row>
   </sheetData>
